--- a/fakedata/excels/test_login.xlsx
+++ b/fakedata/excels/test_login.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOchi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34ECC80-2912-42A6-9186-04CCA281F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A84019-6E2D-4148-A8F1-E2D4B8C5E127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{263407DA-0D41-4A03-A563-3462C2695519}"/>
+    <workbookView xWindow="2213" yWindow="5797" windowWidth="19627" windowHeight="9308" xr2:uid="{263407DA-0D41-4A03-A563-3462C2695519}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"username_or_email":"userfour","password":"testpassword"</t>
+    <t>{
+    "username_or_email": "testuser",
+    "password": "testpassword"
+}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -118,9 +121,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="83.25" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -487,7 +493,7 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H2">
